--- a/assets/translations/Chinese.China.zh-CN.xlsx
+++ b/assets/translations/Chinese.China.zh-CN.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/feiguo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4372BD9-E73C-B547-A0A6-8C5D898F3A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365EA73F-321D-7944-B48A-83DB407F71F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="2420" windowWidth="29400" windowHeight="17220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
     <sheet name="Statements" sheetId="1" r:id="rId2"/>
     <sheet name="Key messages" sheetId="4" r:id="rId3"/>
+    <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
     <author>wang</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="215">
   <si>
     <t>Number</t>
   </si>
@@ -679,13 +680,46 @@
   </si>
   <si>
     <t>0009-0002-1924-7540</t>
+  </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>Consensus statements (Chinese)</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>关键信息</t>
+  </si>
+  <si>
+    <t>参考文献 </t>
+  </si>
+  <si>
+    <t>章节</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>陈述</t>
+  </si>
+  <si>
+    <t>简化陈述</t>
+  </si>
+  <si>
+    <t>背景信息</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -781,6 +815,28 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -796,7 +852,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -850,21 +906,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -966,11 +1007,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -980,22 +1022,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
@@ -1006,10 +1042,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1024,28 +1060,34 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{4C9A585F-509A-1F45-ABE7-6E1BC85D4FC0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1066,9 +1108,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1106,7 +1148,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1212,7 +1254,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1354,7 +1396,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1394,66 +1436,66 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="14" customFormat="1">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:7" s="12" customFormat="1">
+      <c r="A2" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="12" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="14" customFormat="1">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:7" s="12" customFormat="1">
+      <c r="A3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" s="14" customFormat="1">
-      <c r="A4" s="14" t="s">
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" s="12" customFormat="1">
+      <c r="A4" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="14" customFormat="1">
-      <c r="D5" s="11"/>
+    <row r="5" spans="1:7" s="12" customFormat="1">
+      <c r="D5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1469,796 +1511,877 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.5" customWidth="1"/>
     <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="8" width="42.33203125" customWidth="1"/>
-    <col min="9" max="9" width="42.33203125" style="12" customWidth="1"/>
+    <col min="3" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="9" width="42.33203125" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>67</v>
+      <c r="B1" t="s">
+        <v>210</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="13" customFormat="1" ht="85">
+      <c r="J1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="11" customFormat="1" ht="85">
       <c r="A2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="13">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="H2" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="J2" s="21" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="85">
+    <row r="3" spans="1:10" ht="85">
       <c r="A3" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="13">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="13">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="J3" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="102">
+    <row r="4" spans="1:10" ht="119">
       <c r="A4" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>3</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="13">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="H4" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="J4" s="22" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="102">
+    <row r="5" spans="1:10" ht="102">
       <c r="A5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="F5" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="H5" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="J5" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="119">
+    <row r="6" spans="1:10" ht="119">
       <c r="A6" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="F6" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="H6" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="J6" s="21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="68">
+    <row r="7" spans="1:10" ht="68">
       <c r="A7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>6</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="85">
+    <row r="8" spans="1:10" ht="85">
       <c r="A8" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>7</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="F8" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="H8" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="J8" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="85">
+    <row r="9" spans="1:10" ht="85">
       <c r="A9" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>8</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="H9" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="J9" s="21" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34">
+    <row r="10" spans="1:10" ht="51">
       <c r="A10" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>9</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="F10" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="H10" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="J10" s="21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="68">
+    <row r="11" spans="1:10" ht="68">
       <c r="A11" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="F11" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="H11" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="J11" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="102">
+    <row r="12" spans="1:10" ht="102">
       <c r="A12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="F12" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="H12" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="I12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="J12" s="21" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="51">
+    <row r="13" spans="1:10" ht="51">
       <c r="A13" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>12</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="F13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="H13" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="J13" s="21" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="51">
+    <row r="14" spans="1:10" ht="51">
       <c r="A14" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>13</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="F14" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="H14" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="J14" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="85">
+    <row r="15" spans="1:10" ht="85">
       <c r="A15" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>14</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="F15" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="H15" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="J15" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="68">
+    <row r="16" spans="1:10" ht="68">
       <c r="A16" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>15</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="F16" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="H16" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="J16" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="68">
+    <row r="17" spans="1:10" ht="68">
       <c r="A17" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="F17" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="H17" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="J17" s="21" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="51">
+    <row r="18" spans="1:10" ht="51">
       <c r="A18" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>17</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="F18" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="H18" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="J18" s="21" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="68">
+    <row r="19" spans="1:10" ht="68">
       <c r="A19" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>18</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="F19" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="H19" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="23" t="s">
+      <c r="J19" s="21" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="68">
+    <row r="20" spans="1:10" ht="68">
       <c r="A20" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>19</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="F20" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="H20" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="J20" s="21" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="68">
+    <row r="21" spans="1:10" ht="68">
       <c r="A21" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="F21" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="H21" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="I21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="J21" s="21" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="68">
+    <row r="22" spans="1:10" ht="68">
       <c r="A22" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>21</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="F22" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="H22" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="J22" s="21" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="68">
+    <row r="23" spans="1:10" ht="68">
       <c r="A23" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>22</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="F23" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="H23" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="I23" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="J23" s="21" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="51">
+    <row r="24" spans="1:10" ht="51">
       <c r="A24" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>23</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="F24" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="H24" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="J24" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="51">
+    <row r="25" spans="1:10" ht="51">
       <c r="A25" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>24</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="F25" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="H25" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="23" t="s">
+      <c r="J25" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="102">
+    <row r="26" spans="1:10" ht="102">
       <c r="A26" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>25</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="F26" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="H26" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="I26" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="I26" s="23" t="s">
+      <c r="J26" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="120" thickBot="1">
+    <row r="27" spans="1:10" ht="120" thickBot="1">
       <c r="A27" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="7">
         <v>26</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="7">
+        <v>26</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="F27" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G27" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="H27" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="I27" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="25" t="s">
+      <c r="J27" s="23" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2271,7 +2394,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="44.6640625" customWidth="1"/>
@@ -2279,50 +2402,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="63">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="63">
+      <c r="A3" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B3" s="24" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="42">
-      <c r="A3" s="18" t="s">
+    <row r="4" spans="1:4" ht="42">
+      <c r="A4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="63">
-      <c r="A4" s="18" t="s">
+    <row r="5" spans="1:4" ht="63">
+      <c r="A5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B5" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="63">
-      <c r="A5" s="18" t="s">
+    <row r="6" spans="1:4" ht="63">
+      <c r="A6" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B6" s="24" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="63">
-      <c r="A6" s="18" t="s">
+    <row r="7" spans="1:4" ht="63">
+      <c r="A7" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B7" s="24" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2332,4 +2463,43 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A7EC37C-32D1-5E4E-9023-7733BC3AF171}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="25" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="25" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>